--- a/데이터/curriculum.xlsx
+++ b/데이터/curriculum.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0d90a49386c3f612/바탕 화면/AI융개_팀플/데이터/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\AI융개_팀플\데이터\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_0692FB3D5140C329AC836F926EA479DC3720588F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDF19157-8474-4639-BD65-FEEF45C94B2D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8FFB89-1983-4574-9A34-5956E99C4590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AI융합학부" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13703" uniqueCount="745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13703" uniqueCount="746">
   <si>
     <t>연도</t>
   </si>
@@ -2262,6 +2262,10 @@
   </si>
   <si>
     <t>디지털컨텐츠</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>과목명</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2269,7 +2273,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2316,6 +2320,14 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2337,7 +2349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2347,6 +2359,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -25280,8 +25293,11 @@
   </sheetPr>
   <dimension ref="A1:J155"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col min="5" max="5" width="22.54296875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="14">
+    <row r="1" spans="1:10" ht="17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -25294,8 +25310,8 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
+      <c r="E1" s="7" t="s">
+        <v>745</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
@@ -35278,6 +35294,9 @@
   </sheetPr>
   <dimension ref="A1:J154"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col min="5" max="5" width="22.6328125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="14">
       <c r="A1" s="1" t="s">
@@ -39969,6 +39988,9 @@
   </sheetPr>
   <dimension ref="A1:J202"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col min="5" max="5" width="25.36328125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="14">
       <c r="A1" s="1" t="s">
